--- a/artfynd/A 4306-2026 artfynd.xlsx
+++ b/artfynd/A 4306-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131213550</v>
       </c>
       <c r="B2" t="n">
-        <v>58256</v>
+        <v>58258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131213332</v>
       </c>
       <c r="B3" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4306-2026 artfynd.xlsx
+++ b/artfynd/A 4306-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131213550</v>
       </c>
       <c r="B2" t="n">
-        <v>58258</v>
+        <v>58259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131213332</v>
       </c>
       <c r="B3" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4306-2026 artfynd.xlsx
+++ b/artfynd/A 4306-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131213550</v>
       </c>
       <c r="B2" t="n">
-        <v>58259</v>
+        <v>58260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131213332</v>
       </c>
       <c r="B3" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4306-2026 artfynd.xlsx
+++ b/artfynd/A 4306-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131213550</v>
       </c>
       <c r="B2" t="n">
-        <v>58260</v>
+        <v>58263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131213332</v>
       </c>
       <c r="B3" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4306-2026 artfynd.xlsx
+++ b/artfynd/A 4306-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131213550</v>
       </c>
       <c r="B2" t="n">
-        <v>58263</v>
+        <v>58264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131213332</v>
       </c>
       <c r="B3" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4306-2026 artfynd.xlsx
+++ b/artfynd/A 4306-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131213550</v>
       </c>
       <c r="B2" t="n">
-        <v>58264</v>
+        <v>58270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131213332</v>
       </c>
       <c r="B3" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4306-2026 artfynd.xlsx
+++ b/artfynd/A 4306-2026 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>132023032</v>
       </c>
       <c r="B4" t="n">
-        <v>97963</v>
+        <v>97966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4306-2026 artfynd.xlsx
+++ b/artfynd/A 4306-2026 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>132023032</v>
       </c>
       <c r="B4" t="n">
-        <v>97966</v>
+        <v>97974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4306-2026 artfynd.xlsx
+++ b/artfynd/A 4306-2026 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>132023032</v>
       </c>
       <c r="B4" t="n">
-        <v>97974</v>
+        <v>97984</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4306-2026 artfynd.xlsx
+++ b/artfynd/A 4306-2026 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>132023032</v>
       </c>
       <c r="B4" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
